--- a/부채비율_결과.xlsx
+++ b/부채비율_결과.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,66 +424,50 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>부채</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>자본</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>부채비율</t>
+          <t>부채비율(%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A사</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>500</v>
+        <v>92228115000000</v>
       </c>
       <c r="C2" t="n">
-        <v>250</v>
+        <v>363677865000000</v>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>25.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B사</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>300</v>
+        <v>46826413000000</v>
       </c>
       <c r="C3" t="n">
-        <v>400</v>
+        <v>53503752000000</v>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C사</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>700</v>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>700</v>
+        <v>87.52</v>
       </c>
     </row>
   </sheetData>
